--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487705_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487705_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4362</v>
+        <v>7.806</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1409</v>
+        <v>7.4016</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2953</v>
+        <v>0.4043</v>
       </c>
       <c r="G2" t="n">
         <v>6.3337</v>
@@ -610,13 +610,13 @@
         <v>1.9403</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0915</v>
+        <v>-0.7217</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2288</v>
+        <v>0.0319</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8627</v>
+        <v>-0.7537</v>
       </c>
       <c r="V2" t="n">
         <v>1.2239</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.81</v>
+        <v>3.7606</v>
       </c>
       <c r="E3" t="n">
-        <v>7.0255</v>
+        <v>6.085</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.2154</v>
+        <v>-2.3244</v>
       </c>
       <c r="G3" t="n">
         <v>2.4094</v>
@@ -688,13 +688,13 @@
         <v>0.9702</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1767</v>
+        <v>0.1273</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5175</v>
+        <v>0.577</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3407</v>
+        <v>-0.4497</v>
       </c>
       <c r="V3" t="n">
         <v>1.2239</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. GOMA</t>
+          <t>G. TCHIRAKADZE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7703</v>
+        <v>1.7669</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4941</v>
+        <v>1.5381</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7237</v>
+        <v>0.2288</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5609</v>
+        <v>1.3063</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3223</v>
+        <v>-0.3065</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2385</v>
+        <v>1.6127</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9632</v>
+        <v>1.4134</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8414</v>
+        <v>0.6014</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1218</v>
+        <v>0.8119</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4023</v>
+        <v>-0.1071</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5191</v>
+        <v>-0.9079</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1168</v>
+        <v>0.8008</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7761</v>
+        <v>0.5821</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7463</v>
+        <v>0.5821</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2691</v>
+        <v>-0.1214</v>
       </c>
       <c r="T4" t="n">
-        <v>2.5011</v>
+        <v>0.1248</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2319</v>
+        <v>-0.2462</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.8358</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.8358</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. TCHIRAKADZE</t>
+          <t>M. RUBIO CORCHADO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8704</v>
+        <v>1.6043</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7779</v>
+        <v>1.1912</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0925</v>
+        <v>0.4131</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3063</v>
+        <v>0.6408</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3065</v>
+        <v>-1.2094</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6127</v>
+        <v>1.8502</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4134</v>
+        <v>2.0845</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6014</v>
+        <v>0.6179</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8119</v>
+        <v>1.4665</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1071</v>
+        <v>-1.4437</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9079</v>
+        <v>-1.8274</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8008</v>
+        <v>0.3837</v>
       </c>
       <c r="P5" t="n">
         <v>0.5821</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5821</v>
+        <v>2.5224</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0179</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3645</v>
+        <v>0.1531</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3824</v>
+        <v>-0.6656</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.894</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.894</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. RUBIO CORCHADO</t>
+          <t>B. SCHUCH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1407</v>
+        <v>1.5766</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8093</v>
+        <v>1.73</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3314</v>
+        <v>-0.1533</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6408</v>
+        <v>3.7923</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2094</v>
+        <v>1.7046</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8502</v>
+        <v>2.0877</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0845</v>
+        <v>4.3451</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6179</v>
+        <v>2.3686</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4665</v>
+        <v>1.9765</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4437</v>
+        <v>-0.5528999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.8274</v>
+        <v>-0.6641</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3837</v>
+        <v>0.1112</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5821</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9403</v>
+        <v>-2.9105</v>
       </c>
       <c r="R6" t="n">
         <v>2.5224</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9762</v>
+        <v>-0.6037</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2288</v>
+        <v>-0.3166</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7474</v>
+        <v>-0.2871</v>
       </c>
       <c r="V6" t="n">
-        <v>0.894</v>
+        <v>-1.2239</v>
       </c>
       <c r="W6" t="n">
-        <v>0.894</v>
+        <v>0.6119</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.8358</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. SCHUCH</t>
+          <t>G. GOMA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1364</v>
+        <v>0.82</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9082</v>
+        <v>1.6527</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2282</v>
+        <v>-0.8328</v>
       </c>
       <c r="G7" t="n">
-        <v>3.7923</v>
+        <v>1.5609</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7046</v>
+        <v>1.3223</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0877</v>
+        <v>0.2385</v>
       </c>
       <c r="J7" t="n">
-        <v>4.3451</v>
+        <v>1.9632</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3686</v>
+        <v>1.8414</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9765</v>
+        <v>0.1218</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5528999999999999</v>
+        <v>-0.4023</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6641</v>
+        <v>-0.5191</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1112</v>
+        <v>0.1168</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3881</v>
+        <v>0.7761</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5224</v>
+        <v>1.7463</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0439</v>
+        <v>0.3188</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1384</v>
+        <v>0.6597</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0945</v>
+        <v>-0.3409</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2239</v>
+        <v>-1.8358</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6119</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>-1.8358</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0793</v>
+        <v>0.4279</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1577</v>
+        <v>0.1637</v>
       </c>
       <c r="F8" t="n">
-        <v>0.237</v>
+        <v>0.2642</v>
       </c>
       <c r="G8" t="n">
         <v>0.0005999999999999999</v>
@@ -1078,13 +1078,13 @@
         <v>0.7761</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6974</v>
+        <v>-0.3488</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2423</v>
+        <v>0.0791</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4551</v>
+        <v>-0.4279</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. MORENO GUTIERREZ</t>
+          <t>T. VERDERA BENASSAR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1776</v>
+        <v>0.4197</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3293</v>
+        <v>0.2593</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5068</v>
+        <v>0.1604</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6881</v>
+        <v>0.3653</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7637</v>
+        <v>-1.1246</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0756</v>
+        <v>1.4899</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9879</v>
+        <v>1.1739</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0948</v>
+        <v>-0.1936</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8931</v>
+        <v>1.3675</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.676</v>
+        <v>-0.8087</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8585</v>
+        <v>-0.931</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8175</v>
+        <v>0.1223</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5523</v>
+        <v>0.5821</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R9" t="n">
         <v>1.5523</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.382</v>
+        <v>-0.5276999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0011</v>
+        <v>0.0555</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3831</v>
+        <v>-0.5832000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6597</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6597</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. VERDERA BENASSAR</t>
+          <t>F. MORENO GUTIERREZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3505</v>
+        <v>-0.1988</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4019</v>
+        <v>0.3898</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0514</v>
+        <v>-0.5886</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3653</v>
+        <v>-0.6881</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1246</v>
+        <v>-0.7637</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4899</v>
+        <v>0.0756</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1739</v>
+        <v>0.9879</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1936</v>
+        <v>0.0948</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3675</v>
+        <v>0.8931</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8087</v>
+        <v>-1.676</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.931</v>
+        <v>-0.8585</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1223</v>
+        <v>-0.8175</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5821</v>
+        <v>1.5523</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>1.5523</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2979</v>
+        <v>-0.4032</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6057</v>
+        <v>0.0617</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6922</v>
+        <v>-0.4649</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.6597</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.6597</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9133</v>
+        <v>-0.5406</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9581</v>
+        <v>-0.858</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0448</v>
+        <v>0.3173</v>
       </c>
       <c r="G11" t="n">
         <v>-2.7733</v>
@@ -1312,13 +1312,13 @@
         <v>1.5523</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6057</v>
+        <v>-0.233</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0134</v>
+        <v>0.1135</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6191</v>
+        <v>-0.3465</v>
       </c>
       <c r="V11" t="n">
         <v>1.8836</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2076</v>
+        <v>-2.5252</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7917</v>
+        <v>-1.1911</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4158</v>
+        <v>-1.3341</v>
       </c>
       <c r="G12" t="n">
         <v>-1.9653</v>
@@ -1390,13 +1390,13 @@
         <v>0.9702</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9886</v>
+        <v>-0.3062</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5451</v>
+        <v>0.0555</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4435</v>
+        <v>-0.3617</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2239</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.2646</v>
+        <v>-2.6791</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.9509</v>
+        <v>-3.2291</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6863</v>
+        <v>0.55</v>
       </c>
       <c r="G13" t="n">
         <v>-3.2574</v>
@@ -1468,13 +1468,13 @@
         <v>1.7463</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8310999999999999</v>
+        <v>-0.2456</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8479</v>
+        <v>-0.1262</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0168</v>
+        <v>-0.1194</v>
       </c>
       <c r="V13" t="n">
         <v>0.0478</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.3297</v>
+        <v>12.2383</v>
       </c>
       <c r="E14" t="n">
-        <v>14.2249</v>
+        <v>15.1332</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.894799999999999</v>
+        <v>-2.8951</v>
       </c>
       <c r="G14" t="n">
         <v>7.725200000000001</v>
@@ -1522,7 +1522,7 @@
         <v>18.5944</v>
       </c>
       <c r="K14" t="n">
-        <v>4.8857</v>
+        <v>4.885700000000001</v>
       </c>
       <c r="L14" t="n">
         <v>13.7085</v>
@@ -1546,10 +1546,10 @@
         <v>18.4332</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.4864</v>
+        <v>-3.5778</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5606000000000001</v>
+        <v>1.469</v>
       </c>
       <c r="U14" t="n">
         <v>-5.046799999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.132</v>
+        <v>2.0925</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0905</v>
+        <v>2.8903</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9585</v>
+        <v>-0.7978</v>
       </c>
       <c r="G15" t="n">
         <v>-2.2936</v>
@@ -1624,13 +1624,13 @@
         <v>1.3582</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6002999999999999</v>
+        <v>0.5608</v>
       </c>
       <c r="T15" t="n">
-        <v>0.923</v>
+        <v>0.7228</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3228</v>
+        <v>-0.162</v>
       </c>
       <c r="V15" t="n">
         <v>3.4373</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.656</v>
+        <v>1.1071</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7487</v>
+        <v>2.1481</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0927</v>
+        <v>-1.041</v>
       </c>
       <c r="G16" t="n">
         <v>-1.5134</v>
@@ -1702,13 +1702,13 @@
         <v>1.5523</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1097</v>
+        <v>0.5608</v>
       </c>
       <c r="T16" t="n">
-        <v>1.227</v>
+        <v>0.6264</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1173</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>2.4477</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. DIALLO</t>
+          <t>M. RODRIGUEZ MORENO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3686</v>
+        <v>0.3391</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5882</v>
+        <v>0.1602</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.2196</v>
+        <v>0.1789</v>
       </c>
       <c r="G17" t="n">
-        <v>2.2547</v>
+        <v>0.2875</v>
       </c>
       <c r="H17" t="n">
-        <v>2.9322</v>
+        <v>0.1541</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6774</v>
+        <v>0.1335</v>
       </c>
       <c r="J17" t="n">
-        <v>3.7586</v>
+        <v>0.0206</v>
       </c>
       <c r="K17" t="n">
-        <v>3.5962</v>
+        <v>0.0206</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1624</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5038</v>
+        <v>0.2669</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6641</v>
+        <v>0.1335</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8398</v>
+        <v>0.1335</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.9105</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.8806</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9702</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.578</v>
+        <v>0.0516</v>
       </c>
       <c r="T17" t="n">
-        <v>2.4282</v>
+        <v>0.1396</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1499</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.5537</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.8358</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ MORENO</t>
+          <t>D. EBOLO OLU-ELIJAH</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1117</v>
+        <v>-0.6372</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.04</v>
+        <v>1.7322</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1516</v>
+        <v>-2.3694</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2875</v>
+        <v>0.2643</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1541</v>
+        <v>1.2325</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1335</v>
+        <v>-0.9681999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0206</v>
+        <v>4.1148</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0206</v>
+        <v>2.2245</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.8903</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2669</v>
+        <v>-3.8504</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1335</v>
+        <v>-0.992</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1335</v>
+        <v>-2.8585</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.1642</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1759</v>
+        <v>0.8642</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0606</v>
+        <v>0.5473</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1153</v>
+        <v>0.3169</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.9896</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.9896</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. EBOLO OLU-ELIJAH</t>
+          <t>M. DIALLO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2829</v>
+        <v>-0.9177</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7322</v>
+        <v>1.0867</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.0151</v>
+        <v>-2.0044</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2643</v>
+        <v>2.2547</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2325</v>
+        <v>2.9322</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9681999999999999</v>
+        <v>-0.6774</v>
       </c>
       <c r="J19" t="n">
-        <v>4.1148</v>
+        <v>3.7586</v>
       </c>
       <c r="K19" t="n">
-        <v>2.2245</v>
+        <v>3.5962</v>
       </c>
       <c r="L19" t="n">
-        <v>1.8903</v>
+        <v>0.1624</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.8504</v>
+        <v>-1.5038</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.992</v>
+        <v>-0.6641</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.8585</v>
+        <v>-0.8398</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7761</v>
+        <v>-2.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9403</v>
+        <v>-3.8806</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1642</v>
+        <v>0.9702</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2185</v>
+        <v>1.2918</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5473</v>
+        <v>0.9267</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6712</v>
+        <v>0.3651</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9896</v>
+        <v>-1.5537</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.9896</v>
+        <v>0.2821</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.8358</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5532</v>
+        <v>-1.1255</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7616</v>
+        <v>-1.3612</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2084</v>
+        <v>0.2357</v>
       </c>
       <c r="G20" t="n">
         <v>-0.8917</v>
@@ -2014,13 +2014,13 @@
         <v>0.5821</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2734</v>
+        <v>0.1542</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2905</v>
+        <v>0.1099</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0171</v>
+        <v>0.0443</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. DIAZ ZARZUELA</t>
+          <t>A. ARMSTRONG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6534</v>
+        <v>-1.1473</v>
       </c>
       <c r="E21" t="n">
-        <v>2.0582</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.7116</v>
+        <v>-1.1479</v>
       </c>
       <c r="G21" t="n">
-        <v>1.1095</v>
+        <v>-2.1693</v>
       </c>
       <c r="H21" t="n">
-        <v>2.8201</v>
+        <v>1.4393</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.7106</v>
+        <v>-3.6086</v>
       </c>
       <c r="J21" t="n">
-        <v>3.3301</v>
+        <v>0.3963</v>
       </c>
       <c r="K21" t="n">
-        <v>3.2667</v>
+        <v>1.8249</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0634</v>
+        <v>-1.4286</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.2206</v>
+        <v>-2.5656</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4466</v>
+        <v>-0.3856</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.774</v>
+        <v>-2.18</v>
       </c>
       <c r="P21" t="n">
+        <v>0.5821</v>
+      </c>
+      <c r="Q21" t="n">
         <v>-0.9702</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-1.9403</v>
-      </c>
       <c r="R21" t="n">
-        <v>0.9702</v>
+        <v>1.5523</v>
       </c>
       <c r="S21" t="n">
-        <v>0.655</v>
+        <v>0.4399</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6684</v>
+        <v>0.5745</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0134</v>
+        <v>-0.1346</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.4477</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.4477</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. ARMSTRONG</t>
+          <t>F. DIAZ ZARZUELA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9993</v>
+        <v>-1.7535</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4999</v>
+        <v>1.9581</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4994</v>
+        <v>-3.7116</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.1693</v>
+        <v>1.1095</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4393</v>
+        <v>2.8201</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.6086</v>
+        <v>-1.7106</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3963</v>
+        <v>3.3301</v>
       </c>
       <c r="K22" t="n">
-        <v>1.8249</v>
+        <v>3.2667</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.4286</v>
+        <v>0.0634</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.5656</v>
+        <v>-2.2206</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3856</v>
+        <v>-0.4466</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.18</v>
+        <v>-1.774</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5821</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5523</v>
+        <v>0.9702</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4121</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>0.074</v>
+        <v>0.5683</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4861</v>
+        <v>-0.0134</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-2.4477</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9248</v>
+        <v>-2.0061</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6433</v>
+        <v>-0.9426</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2815</v>
+        <v>-1.0635</v>
       </c>
       <c r="G23" t="n">
         <v>1.4049</v>
@@ -2248,13 +2248,13 @@
         <v>0.5821</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0312</v>
+        <v>-0.1124</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7268</v>
+        <v>-0.0261</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3044</v>
+        <v>-0.0863</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.1172</v>
+        <v>-2.7384</v>
       </c>
       <c r="E24" t="n">
         <v>-1.0479</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.0693</v>
+        <v>-1.6906</v>
       </c>
       <c r="G24" t="n">
         <v>-3.0508</v>
@@ -2326,13 +2326,13 @@
         <v>0.7761</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1276</v>
+        <v>0.5064</v>
       </c>
       <c r="T24" t="n">
         <v>0.6079</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4802</v>
+        <v>-0.1015</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.0672</v>
+        <v>-3.8755</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.3301</v>
+        <v>-3.7295</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2629</v>
+        <v>-0.1459</v>
       </c>
       <c r="G25" t="n">
         <v>-3.1271</v>
@@ -2404,13 +2404,13 @@
         <v>1.1642</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0897</v>
+        <v>0.2815</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3511</v>
+        <v>0.2495</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4408</v>
+        <v>0.032</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2239</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-11.3297</v>
+        <v>-10.6625</v>
       </c>
       <c r="E26" t="n">
         <v>2.895</v>
       </c>
       <c r="F26" t="n">
-        <v>-14.2248</v>
+        <v>-13.5575</v>
       </c>
       <c r="G26" t="n">
         <v>-7.725</v>
       </c>
       <c r="H26" t="n">
-        <v>5.8166</v>
+        <v>5.816599999999999</v>
       </c>
       <c r="I26" t="n">
         <v>-13.5415</v>
@@ -2482,13 +2482,13 @@
         <v>10.6719</v>
       </c>
       <c r="S26" t="n">
-        <v>4.486199999999999</v>
+        <v>5.153700000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>5.0468</v>
+        <v>5.046800000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.5604999999999998</v>
+        <v>0.1068999999999999</v>
       </c>
       <c r="V26" t="n">
         <v>-0.3299000000000007</v>
